--- a/data/trans_dic/IP1012-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1012-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -523,7 +524,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que padecen ceguera o problemas de visión</t>
+          <t>Menores que padecen ceguera o problemas de visión (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -677,47 +678,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,59</t>
+          <t>0,0; 3,58</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,43</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,46</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,91</t>
+          <t>0,0; 7,23</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,92</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,82</t>
+          <t>0,0; 1,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,54</t>
+          <t>0,0; 3,35</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 1,02</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -787,12 +788,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0; 0,31</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,38</t>
+          <t>0,15; 1,69</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -802,32 +803,32 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,85</t>
+          <t>0,28; 1,71</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,57</t>
+          <t>0,14; 1,51</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,69</t>
+          <t>0,0; 0,63</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,91</t>
+          <t>0,15; 0,95</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,17</t>
+          <t>0,21; 1,13</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,37</t>
+          <t>0,0; 0,32</t>
         </is>
       </c>
     </row>
@@ -897,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,54</t>
+          <t>0,0; 2,76</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,79</t>
+          <t>0,0; 3,32</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 0,74</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,34</t>
+          <t>0,41; 3,59</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,85</t>
+          <t>0,0; 2,57</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 3,34</t>
+          <t>0,34; 2,97</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,24</t>
+          <t>0,39; 2,21</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,81</t>
+          <t>0,18; 1,98</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,86</t>
+          <t>0,18; 1,61</t>
         </is>
       </c>
     </row>
@@ -1007,7 +1008,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,83</t>
+          <t>0,09; 0,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1022,32 +1023,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,48</t>
+          <t>0,36; 1,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,62</t>
+          <t>0,35; 1,67</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,89</t>
+          <t>0,1; 0,86</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,99</t>
+          <t>0,28; 0,95</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,16</t>
+          <t>0,36; 1,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,46</t>
+          <t>0,05; 0,47</t>
         </is>
       </c>
     </row>
@@ -1071,4 +1072,791 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que padecen ceguera o problemas de visión (tasa de respuesta: 99,78%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="G1" s="3" t="n"/>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>642</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3250</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>0; 6101</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3218</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>0; 5898</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2318</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3723</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2969</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3723</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>5287</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>660; 7604</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1347; 8180</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>696; 7433</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3103</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>1341; 8445</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>2010; 10634</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3098</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>1367</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1272</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>3333</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2197</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4797</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5487</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>644; 5680</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4409</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>645; 5566</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>1301; 7331</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>622; 6664</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>644; 5802</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3243</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6072</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>7698</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>9315</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>629; 5321</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>918; 7671</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>0; 0</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>2617; 11357</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>2625; 12518</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>709; 6374</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>3916; 13350</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>5179; 16260</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>714; 6846</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="C1:E1"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="F1:H1"/>
+    <mergeCell ref="I1:K1"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP1012-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1012-Estudios-trans_dic.xlsx
@@ -698,7 +698,7 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,23</t>
+          <t>0,0; 7,7</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -708,12 +708,12 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,81</t>
+          <t>0,0; 1,82</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,35</t>
+          <t>0,0; 3,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,69</t>
+          <t>0,15; 1,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,28; 1,71</t>
+          <t>0,29; 1,73</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>0,14; 1,51</t>
+          <t>0,14; 1,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,95</t>
+          <t>0,15; 0,93</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,13</t>
+          <t>0,24; 1,19</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -898,12 +898,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,76</t>
+          <t>0,0; 2,73</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,32</t>
+          <t>0,0; 2,99</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -913,32 +913,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 3,59</t>
+          <t>0,41; 3,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,57</t>
+          <t>0,0; 2,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,97</t>
+          <t>0,34; 3,06</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,21</t>
+          <t>0,39; 2,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,98</t>
+          <t>0,18; 1,68</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,61</t>
+          <t>0,18; 1,8</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,78</t>
+          <t>0,09; 0,79</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,09</t>
+          <t>0,13; 1,17</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1023,32 +1023,32 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,57</t>
+          <t>0,37; 1,5</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,35; 1,67</t>
+          <t>0,36; 1,61</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,1; 0,86</t>
+          <t>0,1; 0,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 0,95</t>
+          <t>0,29; 0,93</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,36; 1,12</t>
+          <t>0,37; 1,13</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,47</t>
+          <t>0,05; 0,48</t>
         </is>
       </c>
     </row>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3250</t>
+          <t>0; 3257</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 6101</t>
+          <t>0; 6496</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
@@ -1336,12 +1336,12 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3218</t>
+          <t>0; 3232</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 5898</t>
+          <t>0; 6191</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1474,7 +1474,7 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>660; 7604</t>
+          <t>657; 6310</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1484,32 +1484,32 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1347; 8180</t>
+          <t>1401; 8247</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>696; 7433</t>
+          <t>688; 8125</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0; 3103</t>
+          <t>0; 3101</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1341; 8445</t>
+          <t>1346; 8297</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2010; 10634</t>
+          <t>2257; 11178</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3098</t>
+          <t>0; 3096</t>
         </is>
       </c>
     </row>
@@ -1632,12 +1632,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4797</t>
+          <t>0; 4754</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 5487</t>
+          <t>0; 4937</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -1647,32 +1647,32 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>644; 5680</t>
+          <t>644; 5234</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4409</t>
+          <t>0; 3934</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>645; 5566</t>
+          <t>645; 5739</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1301; 7331</t>
+          <t>1281; 7765</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>622; 6664</t>
+          <t>622; 5644</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>644; 5802</t>
+          <t>644; 6478</t>
         </is>
       </c>
     </row>
@@ -1795,12 +1795,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>629; 5321</t>
+          <t>635; 5399</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>918; 7671</t>
+          <t>922; 8247</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1810,32 +1810,32 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>2617; 11357</t>
+          <t>2652; 10835</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2625; 12518</t>
+          <t>2663; 12022</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>709; 6374</t>
+          <t>723; 6831</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3916; 13350</t>
+          <t>4096; 13066</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5179; 16260</t>
+          <t>5438; 16477</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>714; 6846</t>
+          <t>710; 6957</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP1012-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/IP1012-Estudios-trans_dic.xlsx
@@ -530,14 +530,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -625,27 +625,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,17%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>0,71%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,17%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -678,34 +678,34 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,58</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
+          <t>0,0; 7,91</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 3,59</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 7,7</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
           <t>0,0; 1,82</t>
@@ -713,7 +713,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,51</t>
+          <t>0,0; 3,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -735,32 +735,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>0,78%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0,13%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>0,52%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,78%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>0,13%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -788,47 +788,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>0,32; 1,85</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0,14; 1,57</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 0,69</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0,15; 1,4</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,15; 1,38</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>0,0; 0,0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>0,29; 1,73</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>0,14; 1,65</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 0,63</t>
-        </is>
-      </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,15; 0,93</t>
+          <t>0,15; 0,91</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,24; 1,19</t>
+          <t>0,24; 1,17</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,32</t>
+          <t>0,0; 0,37</t>
         </is>
       </c>
     </row>
@@ -845,32 +845,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0,79%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>0,56%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -898,47 +898,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,73</t>
+          <t>0,41; 3,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,99</t>
+          <t>0,0; 2,85</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>0,34; 3,34</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,54</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 2,79</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>0,41; 3,31</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 2,29</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,34; 3,06</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,34</t>
+          <t>0,39; 2,24</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,68</t>
+          <t>0,18; 1,81</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,18; 1,8</t>
+          <t>0,18; 1,86</t>
         </is>
       </c>
     </row>
@@ -955,32 +955,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,79%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0,81%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,37%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>0,29%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>0,81%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0,37%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1008,47 +1008,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,09; 0,79</t>
+          <t>0,37; 1,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,17</t>
+          <t>0,39; 1,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
+          <t>0,1; 0,89</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0,09; 0,83</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>0,13; 1,09</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 0,0</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,37; 1,5</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,36; 1,61</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>0,1; 0,92</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,93</t>
+          <t>0,29; 0,99</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,13</t>
+          <t>0,34; 1,16</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,48</t>
+          <t>0,05; 0,46</t>
         </is>
       </c>
     </row>
@@ -1105,14 +1105,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -1200,27 +1200,27 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -1253,27 +1253,27 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1831</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
           <t>642</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1831</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -1306,42 +1306,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 3257</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
+          <t>0; 6671</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 3263</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>0; 6496</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 3232</t>
+          <t>0; 3236</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>0; 6191</t>
+          <t>0; 6231</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1363,27 +1363,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr">
         <is>
           <t>3</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -1416,32 +1416,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>3723</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2969</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>618</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>2318</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>3723</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2969</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>618</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1469,47 +1469,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>1516; 8804</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>691; 7752</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3390</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>657; 6310</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>656; 6185</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>0; 0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1401; 8247</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>688; 8125</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0; 3101</t>
-        </is>
-      </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1346; 8297</t>
+          <t>1352; 8124</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2257; 11178</t>
+          <t>2226; 11040</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0; 3096</t>
+          <t>0; 3557</t>
         </is>
       </c>
     </row>
@@ -1526,32 +1526,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1579,32 +1579,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1966</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1272</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2118</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
           <t>1367</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr">
         <is>
           <t>926</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1966</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1272</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>2118</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1632,47 +1632,47 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 4754</t>
+          <t>641; 5288</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4937</t>
+          <t>0; 4890</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
+          <t>646; 6256</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4428</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4618</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>644; 5234</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>0; 3934</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>645; 5739</t>
-        </is>
-      </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>1281; 7765</t>
+          <t>1310; 7427</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>622; 5644</t>
+          <t>617; 6099</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>644; 6478</t>
+          <t>649; 6693</t>
         </is>
       </c>
     </row>
@@ -1689,32 +1689,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -1742,32 +1742,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5689</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>6072</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2736</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>2009</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>3243</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5689</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6072</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>2736</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1795,47 +1795,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>635; 5399</t>
+          <t>2707; 10712</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>922; 8247</t>
+          <t>2913; 12131</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
+          <t>711; 6647</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>634; 5643</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>923; 7739</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
           <t>0; 0</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>2652; 10835</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>2663; 12022</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>723; 6831</t>
-        </is>
-      </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>4096; 13066</t>
+          <t>4003; 13836</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5438; 16477</t>
+          <t>4917; 16908</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>710; 6957</t>
+          <t>712; 6690</t>
         </is>
       </c>
     </row>
